--- a/data/grafik-sanrazryva-2026-10.xlsx
+++ b/data/grafik-sanrazryva-2026-10.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD.MM"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,11 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +49,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -85,6 +108,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A6:AI129"/>
+  <dimension ref="A6:AI144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1168,7 +1203,7 @@
       <c r="B21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1213,7 +1248,7 @@
       <c r="B22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1262,7 +1297,7 @@
       <c r="B23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1311,7 +1346,7 @@
       <c r="B24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1356,12 +1391,12 @@
       <c r="B25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1405,12 +1440,12 @@
       <c r="B26" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1454,12 +1489,12 @@
       <c r="B27" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1503,12 +1538,12 @@
       <c r="B28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1553,12 +1588,12 @@
         <v>9</v>
       </c>
       <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1602,12 +1637,12 @@
         <v>8</v>
       </c>
       <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1651,12 +1686,12 @@
         <v>7</v>
       </c>
       <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1700,12 +1735,12 @@
         <v>6</v>
       </c>
       <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1758,12 +1793,12 @@
         </is>
       </c>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1815,12 +1850,12 @@
         </is>
       </c>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1868,12 +1903,12 @@
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1921,12 +1956,12 @@
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -1979,12 +2014,12 @@
         </is>
       </c>
       <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2036,12 +2071,12 @@
         </is>
       </c>
       <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2093,12 +2128,12 @@
         </is>
       </c>
       <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2160,12 +2195,12 @@
         </is>
       </c>
       <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2225,12 +2260,12 @@
         </is>
       </c>
       <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2290,12 +2325,12 @@
         </is>
       </c>
       <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2364,12 +2399,12 @@
         </is>
       </c>
       <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2437,12 +2472,12 @@
         </is>
       </c>
       <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2506,12 +2541,12 @@
         </is>
       </c>
       <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2549,7 +2584,7 @@
       <c r="B46" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -2580,12 +2615,12 @@
         </is>
       </c>
       <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2622,7 +2657,7 @@
       <c r="B47" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -2653,12 +2688,12 @@
         </is>
       </c>
       <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2700,7 +2735,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -2731,12 +2766,12 @@
         </is>
       </c>
       <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="inlineStr">
+      <c r="K48" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -2777,7 +2812,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -2808,12 +2843,12 @@
         </is>
       </c>
       <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="K49" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -3691,7 +3726,7 @@
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="M70" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -3701,7 +3736,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="O70" s="4" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -3732,12 +3767,12 @@
         </is>
       </c>
       <c r="U70" s="4" t="n"/>
-      <c r="V70" s="4" t="inlineStr">
+      <c r="V70" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="W70" s="4" t="inlineStr">
+      <c r="W70" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -3776,7 +3811,7 @@
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="4" t="n"/>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="M71" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -3786,7 +3821,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="O71" s="4" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -3817,12 +3852,12 @@
         </is>
       </c>
       <c r="U71" s="4" t="n"/>
-      <c r="V71" s="4" t="inlineStr">
+      <c r="V71" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="W71" s="4" t="inlineStr">
+      <c r="W71" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -3858,7 +3893,7 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="N72" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -3868,7 +3903,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="P72" s="4" t="inlineStr">
+      <c r="P72" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -3899,12 +3934,12 @@
         </is>
       </c>
       <c r="V72" s="4" t="n"/>
-      <c r="W72" s="4" t="inlineStr">
+      <c r="W72" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="X72" s="4" t="inlineStr">
+      <c r="X72" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -3939,7 +3974,7 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="N73" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -3949,7 +3984,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="P73" s="4" t="inlineStr">
+      <c r="P73" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -3980,12 +4015,12 @@
         </is>
       </c>
       <c r="V73" s="4" t="n"/>
-      <c r="W73" s="4" t="inlineStr">
+      <c r="W73" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="X73" s="4" t="inlineStr">
+      <c r="X73" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4021,7 +4056,7 @@
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="inlineStr">
+      <c r="O74" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4031,7 +4066,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="Q74" s="4" t="inlineStr">
+      <c r="Q74" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4062,12 +4097,12 @@
         </is>
       </c>
       <c r="W74" s="4" t="n"/>
-      <c r="X74" s="4" t="inlineStr">
+      <c r="X74" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Y74" s="4" t="inlineStr">
+      <c r="Y74" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4102,7 +4137,7 @@
       <c r="L75" s="4" t="n"/>
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
-      <c r="O75" s="4" t="inlineStr">
+      <c r="O75" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4112,7 +4147,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="Q75" s="4" t="inlineStr">
+      <c r="Q75" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4143,12 +4178,12 @@
         </is>
       </c>
       <c r="W75" s="4" t="n"/>
-      <c r="X75" s="4" t="inlineStr">
+      <c r="X75" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Y75" s="4" t="inlineStr">
+      <c r="Y75" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4184,7 +4219,7 @@
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
-      <c r="P76" s="4" t="inlineStr">
+      <c r="P76" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4194,7 +4229,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="R76" s="4" t="inlineStr">
+      <c r="R76" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4225,12 +4260,12 @@
         </is>
       </c>
       <c r="X76" s="4" t="n"/>
-      <c r="Y76" s="4" t="inlineStr">
+      <c r="Y76" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Z76" s="4" t="inlineStr">
+      <c r="Z76" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4265,7 +4300,7 @@
       <c r="M77" s="4" t="n"/>
       <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
-      <c r="P77" s="4" t="inlineStr">
+      <c r="P77" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4275,7 +4310,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="R77" s="4" t="inlineStr">
+      <c r="R77" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4306,12 +4341,12 @@
         </is>
       </c>
       <c r="X77" s="4" t="n"/>
-      <c r="Y77" s="4" t="inlineStr">
+      <c r="Y77" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Z77" s="4" t="inlineStr">
+      <c r="Z77" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4347,7 +4382,7 @@
       <c r="N78" s="4" t="n"/>
       <c r="O78" s="4" t="n"/>
       <c r="P78" s="4" t="n"/>
-      <c r="Q78" s="4" t="inlineStr">
+      <c r="Q78" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4357,7 +4392,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="S78" s="4" t="inlineStr">
+      <c r="S78" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4388,12 +4423,12 @@
         </is>
       </c>
       <c r="Y78" s="4" t="n"/>
-      <c r="Z78" s="4" t="inlineStr">
+      <c r="Z78" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AA78" s="4" t="inlineStr">
+      <c r="AA78" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4428,7 +4463,7 @@
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
       <c r="P79" s="4" t="n"/>
-      <c r="Q79" s="4" t="inlineStr">
+      <c r="Q79" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4438,7 +4473,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="S79" s="4" t="inlineStr">
+      <c r="S79" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4469,12 +4504,12 @@
         </is>
       </c>
       <c r="Y79" s="4" t="n"/>
-      <c r="Z79" s="4" t="inlineStr">
+      <c r="Z79" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AA79" s="4" t="inlineStr">
+      <c r="AA79" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4510,7 +4545,7 @@
       <c r="O80" s="4" t="n"/>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
-      <c r="R80" s="4" t="inlineStr">
+      <c r="R80" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4520,7 +4555,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="T80" s="4" t="inlineStr">
+      <c r="T80" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4551,12 +4586,12 @@
         </is>
       </c>
       <c r="Z80" s="4" t="n"/>
-      <c r="AA80" s="4" t="inlineStr">
+      <c r="AA80" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AB80" s="4" t="inlineStr">
+      <c r="AB80" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4591,7 +4626,7 @@
       <c r="O81" s="4" t="n"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
-      <c r="R81" s="4" t="inlineStr">
+      <c r="R81" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4601,7 +4636,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="T81" s="4" t="inlineStr">
+      <c r="T81" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4632,12 +4667,12 @@
         </is>
       </c>
       <c r="Z81" s="4" t="n"/>
-      <c r="AA81" s="4" t="inlineStr">
+      <c r="AA81" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AB81" s="4" t="inlineStr">
+      <c r="AB81" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4677,7 +4712,7 @@
       <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
       <c r="R82" s="4" t="n"/>
-      <c r="S82" s="4" t="inlineStr">
+      <c r="S82" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4687,7 +4722,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="U82" s="4" t="inlineStr">
+      <c r="U82" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4718,12 +4753,12 @@
         </is>
       </c>
       <c r="AA82" s="4" t="n"/>
-      <c r="AB82" s="4" t="inlineStr">
+      <c r="AB82" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AC82" s="4" t="inlineStr">
+      <c r="AC82" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4762,7 +4797,7 @@
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
       <c r="R83" s="4" t="n"/>
-      <c r="S83" s="4" t="inlineStr">
+      <c r="S83" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4772,7 +4807,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="U83" s="4" t="inlineStr">
+      <c r="U83" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4803,12 +4838,12 @@
         </is>
       </c>
       <c r="AA83" s="4" t="n"/>
-      <c r="AB83" s="4" t="inlineStr">
+      <c r="AB83" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AC83" s="4" t="inlineStr">
+      <c r="AC83" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4844,7 +4879,7 @@
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="inlineStr">
+      <c r="T84" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4854,7 +4889,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="V84" s="4" t="inlineStr">
+      <c r="V84" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4885,12 +4920,12 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="4" t="inlineStr">
+      <c r="AC84" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AD84" s="4" t="inlineStr">
+      <c r="AD84" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -4925,7 +4960,7 @@
       <c r="Q85" s="4" t="n"/>
       <c r="R85" s="4" t="n"/>
       <c r="S85" s="4" t="n"/>
-      <c r="T85" s="4" t="inlineStr">
+      <c r="T85" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -4935,7 +4970,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="V85" s="4" t="inlineStr">
+      <c r="V85" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -4966,12 +5001,12 @@
         </is>
       </c>
       <c r="AB85" s="4" t="n"/>
-      <c r="AC85" s="4" t="inlineStr">
+      <c r="AC85" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AD85" s="4" t="inlineStr">
+      <c r="AD85" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -5008,7 +5043,7 @@
       <c r="S86" s="4" t="n"/>
       <c r="T86" s="4" t="n"/>
       <c r="U86" s="4" t="n"/>
-      <c r="V86" s="4" t="inlineStr">
+      <c r="V86" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5018,7 +5053,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="X86" s="4" t="inlineStr">
+      <c r="X86" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5049,12 +5084,12 @@
         </is>
       </c>
       <c r="AD86" s="4" t="n"/>
-      <c r="AE86" s="4" t="inlineStr">
+      <c r="AE86" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AF86" s="4" t="inlineStr">
+      <c r="AF86" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -5089,7 +5124,7 @@
       <c r="S87" s="4" t="n"/>
       <c r="T87" s="4" t="n"/>
       <c r="U87" s="4" t="n"/>
-      <c r="V87" s="4" t="inlineStr">
+      <c r="V87" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5099,7 +5134,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="X87" s="4" t="inlineStr">
+      <c r="X87" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5130,12 +5165,12 @@
         </is>
       </c>
       <c r="AD87" s="4" t="n"/>
-      <c r="AE87" s="4" t="inlineStr">
+      <c r="AE87" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AF87" s="4" t="inlineStr">
+      <c r="AF87" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -5171,7 +5206,7 @@
       <c r="T88" s="4" t="n"/>
       <c r="U88" s="4" t="n"/>
       <c r="V88" s="4" t="n"/>
-      <c r="W88" s="4" t="inlineStr">
+      <c r="W88" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5181,7 +5216,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="Y88" s="4" t="inlineStr">
+      <c r="Y88" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5212,12 +5247,12 @@
         </is>
       </c>
       <c r="AE88" s="4" t="n"/>
-      <c r="AF88" s="4" t="inlineStr">
+      <c r="AF88" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AG88" s="4" t="inlineStr">
+      <c r="AG88" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -5252,7 +5287,7 @@
       <c r="T89" s="4" t="n"/>
       <c r="U89" s="4" t="n"/>
       <c r="V89" s="4" t="n"/>
-      <c r="W89" s="4" t="inlineStr">
+      <c r="W89" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5262,7 +5297,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="Y89" s="4" t="inlineStr">
+      <c r="Y89" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5293,12 +5328,12 @@
         </is>
       </c>
       <c r="AE89" s="4" t="n"/>
-      <c r="AF89" s="4" t="inlineStr">
+      <c r="AF89" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AG89" s="4" t="inlineStr">
+      <c r="AG89" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
@@ -5334,7 +5369,7 @@
       <c r="U90" s="4" t="n"/>
       <c r="V90" s="4" t="n"/>
       <c r="W90" s="4" t="n"/>
-      <c r="X90" s="4" t="inlineStr">
+      <c r="X90" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5344,7 +5379,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="Z90" s="4" t="inlineStr">
+      <c r="Z90" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5375,7 +5410,7 @@
         </is>
       </c>
       <c r="AF90" s="4" t="n"/>
-      <c r="AG90" s="4" t="inlineStr">
+      <c r="AG90" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
@@ -5411,7 +5446,7 @@
       <c r="U91" s="4" t="n"/>
       <c r="V91" s="4" t="n"/>
       <c r="W91" s="4" t="n"/>
-      <c r="X91" s="4" t="inlineStr">
+      <c r="X91" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5421,7 +5456,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="Z91" s="4" t="inlineStr">
+      <c r="Z91" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5452,7 +5487,7 @@
         </is>
       </c>
       <c r="AF91" s="4" t="n"/>
-      <c r="AG91" s="4" t="inlineStr">
+      <c r="AG91" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
@@ -5489,7 +5524,7 @@
       <c r="V92" s="4" t="n"/>
       <c r="W92" s="4" t="n"/>
       <c r="X92" s="4" t="n"/>
-      <c r="Y92" s="4" t="inlineStr">
+      <c r="Y92" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5499,7 +5534,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AA92" s="4" t="inlineStr">
+      <c r="AA92" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5562,7 +5597,7 @@
       <c r="V93" s="4" t="n"/>
       <c r="W93" s="4" t="n"/>
       <c r="X93" s="4" t="n"/>
-      <c r="Y93" s="4" t="inlineStr">
+      <c r="Y93" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5572,7 +5607,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AA93" s="4" t="inlineStr">
+      <c r="AA93" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5640,7 +5675,7 @@
       <c r="W94" s="4" t="n"/>
       <c r="X94" s="4" t="n"/>
       <c r="Y94" s="4" t="n"/>
-      <c r="Z94" s="4" t="inlineStr">
+      <c r="Z94" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5650,7 +5685,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AB94" s="4" t="inlineStr">
+      <c r="AB94" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5717,7 +5752,7 @@
       <c r="W95" s="4" t="n"/>
       <c r="X95" s="4" t="n"/>
       <c r="Y95" s="4" t="n"/>
-      <c r="Z95" s="4" t="inlineStr">
+      <c r="Z95" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5727,7 +5762,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AB95" s="4" t="inlineStr">
+      <c r="AB95" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5790,7 +5825,7 @@
       <c r="W96" s="4" t="n"/>
       <c r="X96" s="4" t="n"/>
       <c r="Y96" s="4" t="n"/>
-      <c r="Z96" s="4" t="inlineStr">
+      <c r="Z96" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5800,7 +5835,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AB96" s="4" t="inlineStr">
+      <c r="AB96" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5864,7 +5899,7 @@
       <c r="X97" s="4" t="n"/>
       <c r="Y97" s="4" t="n"/>
       <c r="Z97" s="4" t="n"/>
-      <c r="AA97" s="4" t="inlineStr">
+      <c r="AA97" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5874,7 +5909,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AC97" s="4" t="inlineStr">
+      <c r="AC97" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -5937,7 +5972,7 @@
       <c r="X98" s="4" t="n"/>
       <c r="Y98" s="4" t="n"/>
       <c r="Z98" s="4" t="n"/>
-      <c r="AA98" s="4" t="inlineStr">
+      <c r="AA98" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -5947,7 +5982,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AC98" s="4" t="inlineStr">
+      <c r="AC98" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6010,7 +6045,7 @@
       <c r="X99" s="4" t="n"/>
       <c r="Y99" s="4" t="n"/>
       <c r="Z99" s="4" t="n"/>
-      <c r="AA99" s="4" t="inlineStr">
+      <c r="AA99" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6020,7 +6055,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AC99" s="4" t="inlineStr">
+      <c r="AC99" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6080,7 +6115,7 @@
       <c r="Y100" s="4" t="n"/>
       <c r="Z100" s="4" t="n"/>
       <c r="AA100" s="4" t="n"/>
-      <c r="AB100" s="4" t="inlineStr">
+      <c r="AB100" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6090,7 +6125,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AD100" s="4" t="inlineStr">
+      <c r="AD100" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6145,7 +6180,7 @@
       <c r="Y101" s="4" t="n"/>
       <c r="Z101" s="4" t="n"/>
       <c r="AA101" s="4" t="n"/>
-      <c r="AB101" s="4" t="inlineStr">
+      <c r="AB101" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6155,7 +6190,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AD101" s="4" t="inlineStr">
+      <c r="AD101" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6214,7 +6249,7 @@
       <c r="Y102" s="4" t="n"/>
       <c r="Z102" s="4" t="n"/>
       <c r="AA102" s="4" t="n"/>
-      <c r="AB102" s="4" t="inlineStr">
+      <c r="AB102" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6224,7 +6259,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AD102" s="4" t="inlineStr">
+      <c r="AD102" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6284,7 +6319,7 @@
       <c r="Z103" s="4" t="n"/>
       <c r="AA103" s="4" t="n"/>
       <c r="AB103" s="4" t="n"/>
-      <c r="AC103" s="4" t="inlineStr">
+      <c r="AC103" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6294,7 +6329,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AE103" s="4" t="inlineStr">
+      <c r="AE103" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6345,7 +6380,7 @@
       <c r="Z104" s="4" t="n"/>
       <c r="AA104" s="4" t="n"/>
       <c r="AB104" s="4" t="n"/>
-      <c r="AC104" s="4" t="inlineStr">
+      <c r="AC104" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6355,7 +6390,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AE104" s="4" t="inlineStr">
+      <c r="AE104" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6407,7 +6442,7 @@
       <c r="AA105" s="4" t="n"/>
       <c r="AB105" s="4" t="n"/>
       <c r="AC105" s="4" t="n"/>
-      <c r="AD105" s="4" t="inlineStr">
+      <c r="AD105" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6417,7 +6452,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AF105" s="4" t="inlineStr">
+      <c r="AF105" s="7" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
@@ -6468,7 +6503,7 @@
       <c r="AA106" s="4" t="n"/>
       <c r="AB106" s="4" t="n"/>
       <c r="AC106" s="4" t="n"/>
-      <c r="AD106" s="4" t="inlineStr">
+      <c r="AD106" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6478,7 +6513,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AF106" s="4" t="inlineStr">
+      <c r="AF106" s="7" t="inlineStr">
         <is>
           <t>Р/МС</t>
         </is>
@@ -6529,7 +6564,7 @@
       <c r="AA107" s="4" t="n"/>
       <c r="AB107" s="4" t="n"/>
       <c r="AC107" s="4" t="n"/>
-      <c r="AD107" s="4" t="inlineStr">
+      <c r="AD107" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6539,7 +6574,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AF107" s="4" t="inlineStr">
+      <c r="AF107" s="7" t="inlineStr">
         <is>
           <t>Р/МС</t>
         </is>
@@ -6587,7 +6622,7 @@
       <c r="AB108" s="4" t="n"/>
       <c r="AC108" s="4" t="n"/>
       <c r="AD108" s="4" t="n"/>
-      <c r="AE108" s="4" t="inlineStr">
+      <c r="AE108" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6597,7 +6632,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AG108" s="4" t="inlineStr">
+      <c r="AG108" s="7" t="inlineStr">
         <is>
           <t>Р/МС</t>
         </is>
@@ -6640,7 +6675,7 @@
       <c r="AB109" s="4" t="n"/>
       <c r="AC109" s="4" t="n"/>
       <c r="AD109" s="4" t="n"/>
-      <c r="AE109" s="4" t="inlineStr">
+      <c r="AE109" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6650,7 +6685,7 @@
           <t>Р</t>
         </is>
       </c>
-      <c r="AG109" s="4" t="inlineStr">
+      <c r="AG109" s="7" t="inlineStr">
         <is>
           <t>Р/МС</t>
         </is>
@@ -6697,7 +6732,7 @@
       <c r="AB110" s="4" t="n"/>
       <c r="AC110" s="4" t="n"/>
       <c r="AD110" s="4" t="n"/>
-      <c r="AE110" s="4" t="inlineStr">
+      <c r="AE110" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6755,7 +6790,7 @@
       <c r="AC111" s="4" t="n"/>
       <c r="AD111" s="4" t="n"/>
       <c r="AE111" s="4" t="n"/>
-      <c r="AF111" s="4" t="inlineStr">
+      <c r="AF111" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6804,7 +6839,7 @@
       <c r="AC112" s="4" t="n"/>
       <c r="AD112" s="4" t="n"/>
       <c r="AE112" s="4" t="n"/>
-      <c r="AF112" s="4" t="inlineStr">
+      <c r="AF112" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6853,7 +6888,7 @@
       <c r="AC113" s="4" t="n"/>
       <c r="AD113" s="4" t="n"/>
       <c r="AE113" s="4" t="n"/>
-      <c r="AF113" s="4" t="inlineStr">
+      <c r="AF113" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6907,7 +6942,7 @@
       <c r="AD114" s="4" t="n"/>
       <c r="AE114" s="4" t="n"/>
       <c r="AF114" s="4" t="n"/>
-      <c r="AG114" s="4" t="inlineStr">
+      <c r="AG114" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -6956,7 +6991,7 @@
       <c r="AD115" s="4" t="n"/>
       <c r="AE115" s="4" t="n"/>
       <c r="AF115" s="4" t="n"/>
-      <c r="AG115" s="4" t="inlineStr">
+      <c r="AG115" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -7001,7 +7036,7 @@
       <c r="AD116" s="4" t="n"/>
       <c r="AE116" s="4" t="n"/>
       <c r="AF116" s="4" t="n"/>
-      <c r="AG116" s="4" t="inlineStr">
+      <c r="AG116" s="8" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
@@ -7568,6 +7603,230 @@
       </c>
       <c r="AI129" s="4" t="n"/>
     </row>
+    <row r="132">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ос</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>освобождение</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ДС</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>дезинсекция</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>септик обработка</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ОЧ</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>очистка</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>газация формалином</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>обработка дорог</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ОЧН</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>очистка ночь</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ГГ</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>газация глутаркой</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>мойка сутки</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>П</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>побелка день</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>мд</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>мойка ДЕНЬ</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>МН</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>мойка ночь</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ПН</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>побелка ночь</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>р</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>ремонт</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Ш</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>ШАХТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ДЗ</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>дезинфекция</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>подготовка</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>ПР</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>приемка птичника</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ЗО</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>засыпка</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>заселение</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>ЗН</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>засыпка в ночь</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/grafik-sanrazryva-2026-10.xlsx
+++ b/data/grafik-sanrazryva-2026-10.xlsx
@@ -1297,12 +1297,16 @@
       <c r="B23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
@@ -1346,12 +1350,16 @@
       <c r="B24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
@@ -1391,17 +1399,17 @@
       <c r="B25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
@@ -1440,17 +1448,17 @@
       <c r="B26" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="4" t="n"/>
@@ -1489,17 +1497,17 @@
       <c r="B27" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
@@ -1538,17 +1546,17 @@
       <c r="B28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
@@ -1587,18 +1595,22 @@
       <c r="B29" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
@@ -1636,18 +1648,22 @@
       <c r="B30" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
@@ -1685,18 +1701,22 @@
       <c r="B31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
@@ -1734,18 +1754,22 @@
       <c r="B32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
@@ -1789,21 +1813,25 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
@@ -1846,21 +1874,25 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
@@ -1899,21 +1931,25 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
@@ -1952,21 +1988,25 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
@@ -2005,26 +2045,30 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -2062,26 +2106,30 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n"/>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
@@ -2119,26 +2167,30 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n"/>
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
@@ -2176,36 +2228,40 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="n"/>
@@ -2241,36 +2297,40 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="4" t="n"/>
@@ -2306,36 +2366,40 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
           <t>Р\ДС</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ДЗ/ЗОН</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="6" t="inlineStr">
+          <t>ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>ГФ/ОД</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
@@ -2385,12 +2449,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2398,19 +2462,27 @@
           <t>ГФ</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="n"/>
@@ -2458,12 +2530,12 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2471,19 +2543,27 @@
           <t>ГФ</t>
         </is>
       </c>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
@@ -2527,12 +2607,12 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2540,19 +2620,27 @@
           <t>ГФ</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
@@ -2601,12 +2689,12 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2614,19 +2702,27 @@
           <t>ГФ</t>
         </is>
       </c>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
@@ -2674,12 +2770,12 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2687,19 +2783,27 @@
           <t>ГФ</t>
         </is>
       </c>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="n"/>
       <c r="P47" s="4" t="n"/>
@@ -2752,12 +2856,12 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2765,19 +2869,27 @@
           <t>ГФ</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
@@ -2829,12 +2941,12 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2842,19 +2954,27 @@
           <t>ГФ</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
@@ -2884,19 +3004,67 @@
       <c r="B50" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
-      <c r="L50" s="4" t="n"/>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
-      <c r="O50" s="4" t="n"/>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
@@ -2925,19 +3093,67 @@
       <c r="B51" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-      <c r="O51" s="4" t="n"/>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
@@ -2967,19 +3183,67 @@
         <v>10</v>
       </c>
       <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="N52" s="4" t="n"/>
-      <c r="O52" s="4" t="n"/>
-      <c r="P52" s="4" t="n"/>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="Q52" s="4" t="n"/>
       <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
@@ -3008,19 +3272,67 @@
         <v>11</v>
       </c>
       <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="4" t="n"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="N53" s="4" t="n"/>
-      <c r="O53" s="4" t="n"/>
-      <c r="P53" s="4" t="n"/>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
@@ -3050,19 +3362,67 @@
       </c>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
-      <c r="M54" s="4" t="n"/>
-      <c r="N54" s="4" t="n"/>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="O54" s="4" t="n"/>
-      <c r="P54" s="4" t="n"/>
-      <c r="Q54" s="4" t="n"/>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="R54" s="4" t="n"/>
       <c r="S54" s="4" t="n"/>
       <c r="T54" s="4" t="n"/>
@@ -3091,19 +3451,67 @@
       </c>
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="O55" s="4" t="n"/>
-      <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n"/>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
       <c r="T55" s="4" t="n"/>
@@ -3133,19 +3541,67 @@
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
-      <c r="L56" s="4" t="n"/>
-      <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
-      <c r="O56" s="4" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="P56" s="4" t="n"/>
-      <c r="Q56" s="4" t="n"/>
-      <c r="R56" s="4" t="n"/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="S56" s="4" t="n"/>
       <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n"/>
@@ -3174,19 +3630,67 @@
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="n"/>
-      <c r="L57" s="4" t="n"/>
-      <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
-      <c r="O57" s="4" t="n"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="P57" s="4" t="n"/>
-      <c r="Q57" s="4" t="n"/>
-      <c r="R57" s="4" t="n"/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n"/>
@@ -3220,20 +3724,68 @@
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
-      <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
-      <c r="O58" s="4" t="n"/>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n"/>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="R58" s="4" t="n"/>
-      <c r="S58" s="4" t="n"/>
-      <c r="T58" s="4" t="n"/>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="U58" s="4" t="n"/>
       <c r="V58" s="4" t="n"/>
       <c r="W58" s="4" t="n"/>
@@ -3265,20 +3817,68 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="n"/>
-      <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
-      <c r="O59" s="4" t="n"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n"/>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="R59" s="4" t="n"/>
-      <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n"/>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -3307,20 +3907,68 @@
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
-      <c r="O60" s="4" t="n"/>
-      <c r="P60" s="4" t="n"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="Q60" s="4" t="n"/>
-      <c r="R60" s="4" t="n"/>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="S60" s="4" t="n"/>
-      <c r="T60" s="4" t="n"/>
-      <c r="U60" s="4" t="n"/>
+      <c r="T60" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="U60" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="V60" s="4" t="n"/>
       <c r="W60" s="4" t="n"/>
       <c r="X60" s="4" t="n"/>
@@ -3348,20 +3996,68 @@
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
-      <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n"/>
-      <c r="O61" s="4" t="n"/>
-      <c r="P61" s="4" t="n"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="Q61" s="4" t="n"/>
-      <c r="R61" s="4" t="n"/>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
-      <c r="U61" s="4" t="n"/>
+      <c r="T61" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="U61" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
@@ -3390,20 +4086,68 @@
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="n"/>
-      <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
-      <c r="O62" s="4" t="n"/>
-      <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="R62" s="4" t="n"/>
-      <c r="S62" s="4" t="n"/>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="T62" s="4" t="n"/>
-      <c r="U62" s="4" t="n"/>
-      <c r="V62" s="4" t="n"/>
+      <c r="U62" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="V62" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="W62" s="4" t="n"/>
       <c r="X62" s="4" t="n"/>
       <c r="Y62" s="4" t="n"/>
@@ -3431,20 +4175,68 @@
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
-      <c r="L63" s="4" t="n"/>
-      <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
-      <c r="O63" s="4" t="n"/>
-      <c r="P63" s="4" t="n"/>
-      <c r="Q63" s="4" t="n"/>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="R63" s="4" t="n"/>
-      <c r="S63" s="4" t="n"/>
+      <c r="S63" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="T63" s="4" t="n"/>
-      <c r="U63" s="4" t="n"/>
-      <c r="V63" s="4" t="n"/>
+      <c r="U63" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="V63" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="W63" s="4" t="n"/>
       <c r="X63" s="4" t="n"/>
       <c r="Y63" s="4" t="n"/>
@@ -3473,20 +4265,68 @@
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
-      <c r="O64" s="4" t="n"/>
-      <c r="P64" s="4" t="n"/>
-      <c r="Q64" s="4" t="n"/>
-      <c r="R64" s="4" t="n"/>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="R64" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n"/>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="U64" s="4" t="n"/>
-      <c r="V64" s="4" t="n"/>
-      <c r="W64" s="4" t="n"/>
+      <c r="V64" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="W64" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="X64" s="4" t="n"/>
       <c r="Y64" s="4" t="n"/>
       <c r="Z64" s="4" t="n"/>
@@ -3514,20 +4354,68 @@
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
-      <c r="O65" s="4" t="n"/>
-      <c r="P65" s="4" t="n"/>
-      <c r="Q65" s="4" t="n"/>
-      <c r="R65" s="4" t="n"/>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="S65" s="4" t="n"/>
-      <c r="T65" s="4" t="n"/>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="U65" s="4" t="n"/>
-      <c r="V65" s="4" t="n"/>
-      <c r="W65" s="4" t="n"/>
+      <c r="V65" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="W65" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="X65" s="4" t="n"/>
       <c r="Y65" s="4" t="n"/>
       <c r="Z65" s="4" t="n"/>
@@ -3556,20 +4444,68 @@
       <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n"/>
-      <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
-      <c r="O66" s="4" t="n"/>
-      <c r="P66" s="4" t="n"/>
-      <c r="Q66" s="4" t="n"/>
-      <c r="R66" s="4" t="n"/>
-      <c r="S66" s="4" t="n"/>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="S66" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="T66" s="4" t="n"/>
-      <c r="U66" s="4" t="n"/>
+      <c r="U66" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="V66" s="4" t="n"/>
-      <c r="W66" s="4" t="n"/>
-      <c r="X66" s="4" t="n"/>
+      <c r="W66" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="X66" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="Y66" s="4" t="n"/>
       <c r="Z66" s="4" t="n"/>
       <c r="AA66" s="4" t="n"/>
@@ -3597,20 +4533,68 @@
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n"/>
-      <c r="O67" s="4" t="n"/>
-      <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="n"/>
-      <c r="S67" s="4" t="n"/>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="T67" s="4" t="n"/>
-      <c r="U67" s="4" t="n"/>
+      <c r="U67" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="V67" s="4" t="n"/>
-      <c r="W67" s="4" t="n"/>
-      <c r="X67" s="4" t="n"/>
+      <c r="W67" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="X67" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="Y67" s="4" t="n"/>
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
@@ -3639,20 +4623,68 @@
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n"/>
-      <c r="N68" s="4" t="n"/>
-      <c r="O68" s="4" t="n"/>
-      <c r="P68" s="4" t="n"/>
-      <c r="Q68" s="4" t="n"/>
-      <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n"/>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="R68" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="U68" s="4" t="n"/>
-      <c r="V68" s="4" t="n"/>
+      <c r="V68" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="W68" s="4" t="n"/>
-      <c r="X68" s="4" t="n"/>
-      <c r="Y68" s="4" t="n"/>
+      <c r="X68" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="Y68" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="Z68" s="4" t="n"/>
       <c r="AA68" s="4" t="n"/>
       <c r="AB68" s="4" t="n"/>
@@ -3680,20 +4712,68 @@
       <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
-      <c r="L69" s="4" t="n"/>
-      <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
-      <c r="O69" s="4" t="n"/>
-      <c r="P69" s="4" t="n"/>
-      <c r="Q69" s="4" t="n"/>
-      <c r="R69" s="4" t="n"/>
-      <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>Р</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>Р\ДС</t>
+        </is>
+      </c>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="S69" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
       <c r="U69" s="4" t="n"/>
-      <c r="V69" s="4" t="n"/>
+      <c r="V69" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
       <c r="W69" s="4" t="n"/>
-      <c r="X69" s="4" t="n"/>
-      <c r="Y69" s="4" t="n"/>
+      <c r="X69" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ/ОД</t>
+        </is>
+      </c>
+      <c r="Y69" s="5" t="inlineStr">
+        <is>
+          <t>ЗС</t>
+        </is>
+      </c>
       <c r="Z69" s="4" t="n"/>
       <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
@@ -3731,21 +4811,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="P70" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="P70" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -3753,33 +4833,37 @@
       </c>
       <c r="R70" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="S70" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="S70" s="4" t="n"/>
       <c r="T70" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="U70" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="U70" s="4" t="n"/>
-      <c r="V70" s="6" t="inlineStr">
+      <c r="V70" s="4" t="n"/>
+      <c r="W70" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="X70" s="4" t="n"/>
+      <c r="Y70" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="W70" s="5" t="inlineStr">
+      <c r="Z70" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="X70" s="4" t="n"/>
-      <c r="Y70" s="4" t="n"/>
-      <c r="Z70" s="4" t="n"/>
       <c r="AA70" s="4" t="n"/>
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
@@ -3816,21 +4900,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="O71" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="P71" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -3838,33 +4922,37 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="S71" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="S71" s="4" t="n"/>
       <c r="T71" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="U71" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="U71" s="4" t="n"/>
-      <c r="V71" s="6" t="inlineStr">
+      <c r="V71" s="4" t="n"/>
+      <c r="W71" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="X71" s="4" t="n"/>
+      <c r="Y71" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="W71" s="5" t="inlineStr">
+      <c r="Z71" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="X71" s="4" t="n"/>
-      <c r="Y71" s="4" t="n"/>
-      <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
@@ -3898,21 +4986,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="O72" s="4" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="P72" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="R72" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -3920,33 +5008,37 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="T72" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="V72" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="V72" s="4" t="n"/>
-      <c r="W72" s="6" t="inlineStr">
+      <c r="W72" s="4" t="n"/>
+      <c r="X72" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="Y72" s="4" t="n"/>
+      <c r="Z72" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="X72" s="5" t="inlineStr">
+      <c r="AA72" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="Y72" s="4" t="n"/>
-      <c r="Z72" s="4" t="n"/>
-      <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
@@ -3979,21 +5071,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="O73" s="4" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="P73" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4001,33 +5093,37 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="T73" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="V73" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="V73" s="4" t="n"/>
-      <c r="W73" s="6" t="inlineStr">
+      <c r="W73" s="4" t="n"/>
+      <c r="X73" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="Y73" s="4" t="n"/>
+      <c r="Z73" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="X73" s="5" t="inlineStr">
+      <c r="AA73" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="Y73" s="4" t="n"/>
-      <c r="Z73" s="4" t="n"/>
-      <c r="AA73" s="4" t="n"/>
       <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
@@ -4061,21 +5157,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="P74" s="4" t="inlineStr">
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="R74" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Q74" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="R74" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4083,33 +5179,37 @@
       </c>
       <c r="T74" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="U74" s="4" t="n"/>
       <c r="V74" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="W74" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="W74" s="4" t="n"/>
-      <c r="X74" s="6" t="inlineStr">
+      <c r="X74" s="4" t="n"/>
+      <c r="Y74" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="Z74" s="4" t="n"/>
+      <c r="AA74" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Y74" s="5" t="inlineStr">
+      <c r="AB74" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="Z74" s="4" t="n"/>
-      <c r="AA74" s="4" t="n"/>
-      <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
@@ -4142,21 +5242,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="P75" s="4" t="inlineStr">
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="R75" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Q75" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="R75" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4164,33 +5264,37 @@
       </c>
       <c r="T75" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="U75" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="W75" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="W75" s="4" t="n"/>
-      <c r="X75" s="6" t="inlineStr">
+      <c r="X75" s="4" t="n"/>
+      <c r="Y75" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="Z75" s="4" t="n"/>
+      <c r="AA75" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Y75" s="5" t="inlineStr">
+      <c r="AB75" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="4" t="n"/>
-      <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
@@ -4224,21 +5328,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Q76" s="4" t="inlineStr">
+      <c r="Q76" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="R76" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="S76" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="R76" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="S76" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="T76" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4246,33 +5350,37 @@
       </c>
       <c r="U76" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="V76" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="X76" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="X76" s="4" t="n"/>
-      <c r="Y76" s="6" t="inlineStr">
+      <c r="Y76" s="4" t="n"/>
+      <c r="Z76" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="AA76" s="4" t="n"/>
+      <c r="AB76" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Z76" s="5" t="inlineStr">
+      <c r="AC76" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AA76" s="4" t="n"/>
-      <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
       <c r="AF76" s="4" t="n"/>
@@ -4305,21 +5413,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Q77" s="4" t="inlineStr">
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="S77" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="R77" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="S77" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="T77" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4327,33 +5435,37 @@
       </c>
       <c r="U77" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="V77" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="V77" s="4" t="n"/>
       <c r="W77" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="X77" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="X77" s="4" t="n"/>
-      <c r="Y77" s="6" t="inlineStr">
+      <c r="Y77" s="4" t="n"/>
+      <c r="Z77" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="AA77" s="4" t="n"/>
+      <c r="AB77" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Z77" s="5" t="inlineStr">
+      <c r="AC77" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AA77" s="4" t="n"/>
-      <c r="AB77" s="4" t="n"/>
-      <c r="AC77" s="4" t="n"/>
       <c r="AD77" s="4" t="n"/>
       <c r="AE77" s="4" t="n"/>
       <c r="AF77" s="4" t="n"/>
@@ -4387,21 +5499,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="R78" s="4" t="inlineStr">
+      <c r="R78" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="S78" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="T78" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="S78" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="T78" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="U78" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4409,33 +5521,37 @@
       </c>
       <c r="V78" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="W78" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="W78" s="4" t="n"/>
       <c r="X78" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="Y78" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Y78" s="4" t="n"/>
-      <c r="Z78" s="6" t="inlineStr">
+      <c r="Z78" s="4" t="n"/>
+      <c r="AA78" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="AB78" s="4" t="n"/>
+      <c r="AC78" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AA78" s="5" t="inlineStr">
+      <c r="AD78" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AB78" s="4" t="n"/>
-      <c r="AC78" s="4" t="n"/>
-      <c r="AD78" s="4" t="n"/>
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
       <c r="AG78" s="4" t="n"/>
@@ -4468,21 +5584,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="R79" s="4" t="inlineStr">
+      <c r="R79" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="S79" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="T79" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="T79" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="U79" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4490,33 +5606,37 @@
       </c>
       <c r="V79" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="W79" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="W79" s="4" t="n"/>
       <c r="X79" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="Y79" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Y79" s="4" t="n"/>
-      <c r="Z79" s="6" t="inlineStr">
+      <c r="Z79" s="4" t="n"/>
+      <c r="AA79" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="AB79" s="4" t="n"/>
+      <c r="AC79" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AA79" s="5" t="inlineStr">
+      <c r="AD79" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AB79" s="4" t="n"/>
-      <c r="AC79" s="4" t="n"/>
-      <c r="AD79" s="4" t="n"/>
       <c r="AE79" s="4" t="n"/>
       <c r="AF79" s="4" t="n"/>
       <c r="AG79" s="4" t="n"/>
@@ -4550,21 +5670,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="S80" s="4" t="inlineStr">
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="T80" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="U80" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="T80" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="V80" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4572,33 +5692,37 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="X80" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="X80" s="4" t="n"/>
       <c r="Y80" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="Z80" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Z80" s="4" t="n"/>
-      <c r="AA80" s="6" t="inlineStr">
+      <c r="AA80" s="4" t="n"/>
+      <c r="AB80" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="AC80" s="4" t="n"/>
+      <c r="AD80" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AB80" s="5" t="inlineStr">
+      <c r="AE80" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AC80" s="4" t="n"/>
-      <c r="AD80" s="4" t="n"/>
-      <c r="AE80" s="4" t="n"/>
       <c r="AF80" s="4" t="n"/>
       <c r="AG80" s="4" t="n"/>
       <c r="AH80" s="4" t="n">
@@ -4631,21 +5755,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="S81" s="4" t="inlineStr">
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="T81" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="U81" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="T81" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="U81" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="V81" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4653,33 +5777,37 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
-        </is>
-      </c>
-      <c r="X81" s="4" t="inlineStr">
-        <is>
-          <t>ДЗ/ГГ</t>
-        </is>
-      </c>
+          <t>ДЗ/ПН</t>
+        </is>
+      </c>
+      <c r="X81" s="4" t="n"/>
       <c r="Y81" s="4" t="inlineStr">
         <is>
+          <t>ЗО/ДЗ/ГГ/СО</t>
+        </is>
+      </c>
+      <c r="Z81" s="4" t="inlineStr">
+        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Z81" s="4" t="n"/>
-      <c r="AA81" s="6" t="inlineStr">
+      <c r="AA81" s="4" t="n"/>
+      <c r="AB81" s="4" t="inlineStr">
+        <is>
+          <t>СО</t>
+        </is>
+      </c>
+      <c r="AC81" s="4" t="n"/>
+      <c r="AD81" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AB81" s="5" t="inlineStr">
+      <c r="AE81" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AC81" s="4" t="n"/>
-      <c r="AD81" s="4" t="n"/>
-      <c r="AE81" s="4" t="n"/>
       <c r="AF81" s="4" t="n"/>
       <c r="AG81" s="4" t="n"/>
       <c r="AH81" s="4" t="n">
@@ -4717,21 +5845,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="T82" s="4" t="inlineStr">
+      <c r="T82" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="U82" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="V82" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="U82" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4739,12 +5867,12 @@
       </c>
       <c r="X82" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="Z82" s="4" t="inlineStr">
@@ -4753,19 +5881,23 @@
         </is>
       </c>
       <c r="AA82" s="4" t="n"/>
-      <c r="AB82" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AC82" s="5" t="inlineStr">
+      <c r="AB82" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AC82" s="4" t="n"/>
+      <c r="AD82" s="4" t="n"/>
+      <c r="AE82" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="AF82" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AD82" s="4" t="n"/>
-      <c r="AE82" s="4" t="n"/>
-      <c r="AF82" s="4" t="n"/>
       <c r="AG82" s="4" t="n"/>
       <c r="AH82" s="4" t="n">
         <v>1</v>
@@ -4802,21 +5934,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="T83" s="4" t="inlineStr">
+      <c r="T83" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="U83" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="V83" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="U83" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="V83" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4824,12 +5956,12 @@
       </c>
       <c r="X83" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="Y83" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="Z83" s="4" t="inlineStr">
@@ -4838,19 +5970,23 @@
         </is>
       </c>
       <c r="AA83" s="4" t="n"/>
-      <c r="AB83" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AC83" s="5" t="inlineStr">
+      <c r="AB83" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AC83" s="4" t="n"/>
+      <c r="AD83" s="4" t="n"/>
+      <c r="AE83" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="AF83" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AD83" s="4" t="n"/>
-      <c r="AE83" s="4" t="n"/>
-      <c r="AF83" s="4" t="n"/>
       <c r="AG83" s="4" t="n"/>
       <c r="AH83" s="4" t="n">
         <v>2</v>
@@ -4884,21 +6020,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="U84" s="4" t="inlineStr">
+      <c r="U84" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="V84" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="W84" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="V84" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="W84" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="X84" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4906,12 +6042,12 @@
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="Z84" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AA84" s="4" t="inlineStr">
@@ -4920,19 +6056,23 @@
         </is>
       </c>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AD84" s="5" t="inlineStr">
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AD84" s="4" t="n"/>
+      <c r="AE84" s="4" t="n"/>
+      <c r="AF84" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="AG84" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AE84" s="4" t="n"/>
-      <c r="AF84" s="4" t="n"/>
-      <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n">
         <v>3</v>
       </c>
@@ -4965,21 +6105,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="U85" s="4" t="inlineStr">
+      <c r="U85" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="V85" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="W85" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="V85" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="W85" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="X85" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -4987,12 +6127,12 @@
       </c>
       <c r="Y85" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="Z85" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AA85" s="4" t="inlineStr">
@@ -5001,19 +6141,23 @@
         </is>
       </c>
       <c r="AB85" s="4" t="n"/>
-      <c r="AC85" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AD85" s="5" t="inlineStr">
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AD85" s="4" t="n"/>
+      <c r="AE85" s="4" t="n"/>
+      <c r="AF85" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="AG85" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="AE85" s="4" t="n"/>
-      <c r="AF85" s="4" t="n"/>
-      <c r="AG85" s="4" t="n"/>
       <c r="AH85" s="4" t="n">
         <v>4</v>
       </c>
@@ -5048,21 +6192,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="W86" s="4" t="inlineStr">
+      <c r="W86" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="X86" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="Y86" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="X86" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="Y86" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="Z86" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5070,12 +6214,12 @@
       </c>
       <c r="AA86" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AB86" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AC86" s="4" t="inlineStr">
@@ -5084,16 +6228,12 @@
         </is>
       </c>
       <c r="AD86" s="4" t="n"/>
-      <c r="AE86" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AF86" s="5" t="inlineStr">
-        <is>
-          <t>ЗС</t>
-        </is>
-      </c>
+      <c r="AE86" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AF86" s="4" t="n"/>
       <c r="AG86" s="4" t="n"/>
       <c r="AH86" s="4" t="n">
         <v>5</v>
@@ -5129,21 +6269,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="W87" s="4" t="inlineStr">
+      <c r="W87" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="X87" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="Y87" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="X87" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="Y87" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="Z87" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5151,12 +6291,12 @@
       </c>
       <c r="AA87" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AB87" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AC87" s="4" t="inlineStr">
@@ -5165,16 +6305,12 @@
         </is>
       </c>
       <c r="AD87" s="4" t="n"/>
-      <c r="AE87" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AF87" s="5" t="inlineStr">
-        <is>
-          <t>ЗС</t>
-        </is>
-      </c>
+      <c r="AE87" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AF87" s="4" t="n"/>
       <c r="AG87" s="4" t="n"/>
       <c r="AH87" s="4" t="n">
         <v>6</v>
@@ -5211,21 +6347,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="X88" s="4" t="inlineStr">
+      <c r="X88" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="Y88" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="Z88" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Y88" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="Z88" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="AA88" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5233,12 +6369,12 @@
       </c>
       <c r="AB88" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AD88" s="4" t="inlineStr">
@@ -5247,16 +6383,12 @@
         </is>
       </c>
       <c r="AE88" s="4" t="n"/>
-      <c r="AF88" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AG88" s="5" t="inlineStr">
-        <is>
-          <t>ЗС</t>
-        </is>
-      </c>
+      <c r="AF88" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AG88" s="4" t="n"/>
       <c r="AH88" s="4" t="n">
         <v>7</v>
       </c>
@@ -5292,21 +6424,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="X89" s="4" t="inlineStr">
+      <c r="X89" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="Y89" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="Z89" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Y89" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="Z89" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="AA89" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5314,12 +6446,12 @@
       </c>
       <c r="AB89" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AC89" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AD89" s="4" t="inlineStr">
@@ -5328,16 +6460,12 @@
         </is>
       </c>
       <c r="AE89" s="4" t="n"/>
-      <c r="AF89" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="AG89" s="5" t="inlineStr">
-        <is>
-          <t>ЗС</t>
-        </is>
-      </c>
+      <c r="AF89" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="AG89" s="4" t="n"/>
       <c r="AH89" s="4" t="n">
         <v>8</v>
       </c>
@@ -5374,21 +6502,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Y90" s="4" t="inlineStr">
+      <c r="Y90" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="Z90" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="AA90" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Z90" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="AA90" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="AB90" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5396,12 +6524,12 @@
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AD90" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AE90" s="4" t="inlineStr">
@@ -5410,9 +6538,9 @@
         </is>
       </c>
       <c r="AF90" s="4" t="n"/>
-      <c r="AG90" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
+      <c r="AG90" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
         </is>
       </c>
       <c r="AH90" s="4" t="n">
@@ -5451,21 +6579,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Y91" s="4" t="inlineStr">
+      <c r="Y91" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="Z91" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="AA91" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="Z91" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="AA91" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="AB91" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5473,12 +6601,12 @@
       </c>
       <c r="AC91" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AD91" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AE91" s="4" t="inlineStr">
@@ -5487,9 +6615,9 @@
         </is>
       </c>
       <c r="AF91" s="4" t="n"/>
-      <c r="AG91" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
+      <c r="AG91" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
         </is>
       </c>
       <c r="AH91" s="4" t="n">
@@ -5529,21 +6657,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Z92" s="4" t="inlineStr">
+      <c r="Z92" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="AA92" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="AB92" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="AA92" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="AB92" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5551,12 +6679,12 @@
       </c>
       <c r="AD92" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AE92" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AF92" s="4" t="inlineStr">
@@ -5602,21 +6730,21 @@
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="Z93" s="4" t="inlineStr">
+      <c r="Z93" s="7" t="inlineStr">
+        <is>
+          <t>МС</t>
+        </is>
+      </c>
+      <c r="AA93" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
+      <c r="AB93" s="4" t="inlineStr">
         <is>
           <t>Р</t>
         </is>
       </c>
-      <c r="AA93" s="7" t="inlineStr">
-        <is>
-          <t>МС</t>
-        </is>
-      </c>
-      <c r="AB93" s="4" t="inlineStr">
-        <is>
-          <t>ПР/Р</t>
-        </is>
-      </c>
       <c r="AC93" s="4" t="inlineStr">
         <is>
           <t>Р\ДС</t>
@@ -5624,12 +6752,12 @@
       </c>
       <c r="AD93" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗН</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="AE93" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ</t>
+          <t>ЗО/ДЗ/ГГ</t>
         </is>
       </c>
       <c r="AF93" s="4" t="inlineStr">

--- a/data/grafik-sanrazryva-2026-10.xlsx
+++ b/data/grafik-sanrazryva-2026-10.xlsx
@@ -1297,16 +1297,12 @@
       <c r="B23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
@@ -1350,17 +1346,17 @@
       <c r="B24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
@@ -1595,22 +1591,18 @@
       <c r="B29" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
@@ -1648,22 +1640,18 @@
       <c r="B30" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
@@ -1701,22 +1689,18 @@
       <c r="B31" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
@@ -1754,22 +1738,18 @@
       <c r="B32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>ПДГ</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
@@ -1813,25 +1793,25 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
@@ -1874,25 +1854,25 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
@@ -1931,25 +1911,25 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
@@ -1988,25 +1968,25 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
@@ -2045,30 +2025,30 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -2106,30 +2086,30 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="H38" s="4" t="n"/>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
@@ -2167,30 +2147,30 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ЗОН</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ГФ</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>ПДГ/ОД</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
+          <t>ОД</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>ПДГ</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="H39" s="4" t="n"/>
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
@@ -2243,18 +2223,22 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n"/>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>ПДГ/ОД</t>
+          <t>ПДГ</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -2312,18 +2296,22 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n"/>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>ПДГ/ОД</t>
+          <t>ПДГ</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2381,18 +2369,22 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ГГ/СО</t>
+          <t>ДЗ/ГГ</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>ГФ/ОД</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n"/>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>ОД</t>
+        </is>
+      </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>ПДГ/ОД</t>
+          <t>ПДГ</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -4836,34 +4828,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="S70" s="4" t="n"/>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="T70" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="U70" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="V70" s="4" t="n"/>
-      <c r="W70" s="4" t="inlineStr">
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="X70" s="4" t="n"/>
-      <c r="Y70" s="6" t="inlineStr">
+      <c r="W70" s="4" t="n"/>
+      <c r="X70" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Z70" s="5" t="inlineStr">
+      <c r="Y70" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Z70" s="4" t="n"/>
       <c r="AA70" s="4" t="n"/>
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
@@ -4925,34 +4917,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="S71" s="4" t="n"/>
+      <c r="S71" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="T71" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="U71" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="V71" s="4" t="n"/>
-      <c r="W71" s="4" t="inlineStr">
+      <c r="U71" s="4" t="n"/>
+      <c r="V71" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="X71" s="4" t="n"/>
-      <c r="Y71" s="6" t="inlineStr">
+      <c r="W71" s="4" t="n"/>
+      <c r="X71" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="Z71" s="5" t="inlineStr">
+      <c r="Y71" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="4" t="n"/>
@@ -5011,34 +5003,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="T72" s="4" t="n"/>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="U72" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="V72" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="W72" s="4" t="n"/>
-      <c r="X72" s="4" t="inlineStr">
+      <c r="V72" s="4" t="n"/>
+      <c r="W72" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="Y72" s="4" t="n"/>
-      <c r="Z72" s="6" t="inlineStr">
+      <c r="X72" s="4" t="n"/>
+      <c r="Y72" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AA72" s="5" t="inlineStr">
+      <c r="Z72" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
@@ -5096,34 +5088,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="T73" s="4" t="n"/>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="U73" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="V73" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="W73" s="4" t="n"/>
-      <c r="X73" s="4" t="inlineStr">
+      <c r="V73" s="4" t="n"/>
+      <c r="W73" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="Y73" s="4" t="n"/>
-      <c r="Z73" s="6" t="inlineStr">
+      <c r="X73" s="4" t="n"/>
+      <c r="Y73" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AA73" s="5" t="inlineStr">
+      <c r="Z73" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AA73" s="4" t="n"/>
       <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
@@ -5182,34 +5174,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="U74" s="4" t="n"/>
+      <c r="U74" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="V74" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="W74" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="X74" s="4" t="n"/>
-      <c r="Y74" s="4" t="inlineStr">
+      <c r="W74" s="4" t="n"/>
+      <c r="X74" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="Z74" s="4" t="n"/>
-      <c r="AA74" s="6" t="inlineStr">
+      <c r="Y74" s="4" t="n"/>
+      <c r="Z74" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AB74" s="5" t="inlineStr">
+      <c r="AA74" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
@@ -5267,34 +5259,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="U75" s="4" t="n"/>
+      <c r="U75" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="V75" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="W75" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="X75" s="4" t="n"/>
-      <c r="Y75" s="4" t="inlineStr">
+      <c r="W75" s="4" t="n"/>
+      <c r="X75" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="6" t="inlineStr">
+      <c r="Y75" s="4" t="n"/>
+      <c r="Z75" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AB75" s="5" t="inlineStr">
+      <c r="AA75" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
@@ -5353,34 +5345,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="V76" s="4" t="n"/>
+      <c r="V76" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="X76" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Y76" s="4" t="n"/>
-      <c r="Z76" s="4" t="inlineStr">
+      <c r="X76" s="4" t="n"/>
+      <c r="Y76" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="AA76" s="4" t="n"/>
-      <c r="AB76" s="6" t="inlineStr">
+      <c r="Z76" s="4" t="n"/>
+      <c r="AA76" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AC76" s="5" t="inlineStr">
+      <c r="AB76" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
       <c r="AF76" s="4" t="n"/>
@@ -5438,34 +5430,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="V77" s="4" t="n"/>
+      <c r="V77" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="X77" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Y77" s="4" t="n"/>
-      <c r="Z77" s="4" t="inlineStr">
+      <c r="X77" s="4" t="n"/>
+      <c r="Y77" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="AA77" s="4" t="n"/>
-      <c r="AB77" s="6" t="inlineStr">
+      <c r="Z77" s="4" t="n"/>
+      <c r="AA77" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AC77" s="5" t="inlineStr">
+      <c r="AB77" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AC77" s="4" t="n"/>
       <c r="AD77" s="4" t="n"/>
       <c r="AE77" s="4" t="n"/>
       <c r="AF77" s="4" t="n"/>
@@ -5524,34 +5516,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="W78" s="4" t="n"/>
+      <c r="W78" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="X78" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="Y78" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Z78" s="4" t="n"/>
-      <c r="AA78" s="4" t="inlineStr">
+      <c r="Y78" s="4" t="n"/>
+      <c r="Z78" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="AB78" s="4" t="n"/>
-      <c r="AC78" s="6" t="inlineStr">
+      <c r="AA78" s="4" t="n"/>
+      <c r="AB78" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AD78" s="5" t="inlineStr">
+      <c r="AC78" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AD78" s="4" t="n"/>
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
       <c r="AG78" s="4" t="n"/>
@@ -5609,34 +5601,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="W79" s="4" t="n"/>
+      <c r="W79" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="X79" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="Y79" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="Z79" s="4" t="n"/>
-      <c r="AA79" s="4" t="inlineStr">
+      <c r="Y79" s="4" t="n"/>
+      <c r="Z79" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="AB79" s="4" t="n"/>
-      <c r="AC79" s="6" t="inlineStr">
+      <c r="AA79" s="4" t="n"/>
+      <c r="AB79" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AD79" s="5" t="inlineStr">
+      <c r="AC79" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AD79" s="4" t="n"/>
       <c r="AE79" s="4" t="n"/>
       <c r="AF79" s="4" t="n"/>
       <c r="AG79" s="4" t="n"/>
@@ -5695,34 +5687,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="X80" s="4" t="n"/>
+      <c r="X80" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="Z80" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="AA80" s="4" t="n"/>
-      <c r="AB80" s="4" t="inlineStr">
+      <c r="Z80" s="4" t="n"/>
+      <c r="AA80" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="AC80" s="4" t="n"/>
-      <c r="AD80" s="6" t="inlineStr">
+      <c r="AB80" s="4" t="n"/>
+      <c r="AC80" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AE80" s="5" t="inlineStr">
+      <c r="AD80" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AE80" s="4" t="n"/>
       <c r="AF80" s="4" t="n"/>
       <c r="AG80" s="4" t="n"/>
       <c r="AH80" s="4" t="n">
@@ -5780,34 +5772,34 @@
           <t>ДЗ/ПН</t>
         </is>
       </c>
-      <c r="X81" s="4" t="n"/>
+      <c r="X81" s="4" t="inlineStr">
+        <is>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
       <c r="Y81" s="4" t="inlineStr">
         <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
-      <c r="Z81" s="4" t="inlineStr">
-        <is>
           <t>ГФ</t>
         </is>
       </c>
-      <c r="AA81" s="4" t="n"/>
-      <c r="AB81" s="4" t="inlineStr">
+      <c r="Z81" s="4" t="n"/>
+      <c r="AA81" s="4" t="inlineStr">
         <is>
           <t>СО</t>
         </is>
       </c>
-      <c r="AC81" s="4" t="n"/>
-      <c r="AD81" s="6" t="inlineStr">
+      <c r="AB81" s="4" t="n"/>
+      <c r="AC81" s="6" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="AE81" s="5" t="inlineStr">
+      <c r="AD81" s="5" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="AE81" s="4" t="n"/>
       <c r="AF81" s="4" t="n"/>
       <c r="AG81" s="4" t="n"/>
       <c r="AH81" s="4" t="n">
